--- a/circuits/PumpControl_100x100/XGerber/ESP_PumpControl_CPL.xlsx
+++ b/circuits/PumpControl_100x100/XGerber/ESP_PumpControl_CPL.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <si>
     <t>Designator</t>
   </si>
@@ -46,10 +46,145 @@
     <t>0.0</t>
   </si>
   <si>
+    <t>J3</t>
+  </si>
+  <si>
+    <t>63.9mm</t>
+  </si>
+  <si>
+    <t>10.99mm</t>
+  </si>
+  <si>
+    <t>Top</t>
+  </si>
+  <si>
+    <t>270.0</t>
+  </si>
+  <si>
+    <t>J7</t>
+  </si>
+  <si>
+    <t>65.5mm</t>
+  </si>
+  <si>
+    <t>38.21mm</t>
+  </si>
+  <si>
+    <t>Top</t>
+  </si>
+  <si>
+    <t>90.0</t>
+  </si>
+  <si>
+    <t>J8</t>
+  </si>
+  <si>
+    <t>65.6mm</t>
+  </si>
+  <si>
+    <t>26.21mm</t>
+  </si>
+  <si>
+    <t>Top</t>
+  </si>
+  <si>
+    <t>90.0</t>
+  </si>
+  <si>
+    <t>J9</t>
+  </si>
+  <si>
+    <t>49.5mm</t>
+  </si>
+  <si>
+    <t>2.3mm</t>
+  </si>
+  <si>
+    <t>Top</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>J6</t>
+  </si>
+  <si>
+    <t>9.15mm</t>
+  </si>
+  <si>
+    <t>1.7mm</t>
+  </si>
+  <si>
+    <t>Top</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>X1</t>
+  </si>
+  <si>
+    <t>28.155mm</t>
+  </si>
+  <si>
+    <t>71.135mm</t>
+  </si>
+  <si>
+    <t>Top</t>
+  </si>
+  <si>
+    <t>270.0</t>
+  </si>
+  <si>
+    <t>K2</t>
+  </si>
+  <si>
+    <t>60.5mm</t>
+  </si>
+  <si>
+    <t>51.0mm</t>
+  </si>
+  <si>
+    <t>Top</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>IC2</t>
+  </si>
+  <si>
+    <t>49.7mm</t>
+  </si>
+  <si>
+    <t>23.525mm</t>
+  </si>
+  <si>
+    <t>Top</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>IC1</t>
+  </si>
+  <si>
+    <t>13.8mm</t>
+  </si>
+  <si>
+    <t>35.525mm</t>
+  </si>
+  <si>
+    <t>Top</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
     <t>J2</t>
   </si>
   <si>
-    <t>63.9mm</t>
+    <t>66.4mm</t>
   </si>
   <si>
     <t>10.99mm</t>
@@ -61,13 +196,73 @@
     <t>270.0</t>
   </si>
   <si>
-    <t>J6</t>
-  </si>
-  <si>
-    <t>65.5mm</t>
-  </si>
-  <si>
-    <t>38.21mm</t>
+    <t>J4</t>
+  </si>
+  <si>
+    <t>61.4mm</t>
+  </si>
+  <si>
+    <t>10.99mm</t>
+  </si>
+  <si>
+    <t>Top</t>
+  </si>
+  <si>
+    <t>270.0</t>
+  </si>
+  <si>
+    <t>J5</t>
+  </si>
+  <si>
+    <t>58.9mm</t>
+  </si>
+  <si>
+    <t>10.99mm</t>
+  </si>
+  <si>
+    <t>Top</t>
+  </si>
+  <si>
+    <t>270.0</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>4.1mm</t>
+  </si>
+  <si>
+    <t>72.3mm</t>
+  </si>
+  <si>
+    <t>Bottom</t>
+  </si>
+  <si>
+    <t>270.0</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>7.1mm</t>
+  </si>
+  <si>
+    <t>72.1mm</t>
+  </si>
+  <si>
+    <t>Top</t>
+  </si>
+  <si>
+    <t>270.0</t>
+  </si>
+  <si>
+    <t>X2</t>
+  </si>
+  <si>
+    <t>24.49mm</t>
+  </si>
+  <si>
+    <t>71.12mm</t>
   </si>
   <si>
     <t>Top</t>
@@ -76,169 +271,34 @@
     <t>90.0</t>
   </si>
   <si>
-    <t>J7</t>
-  </si>
-  <si>
-    <t>65.6mm</t>
-  </si>
-  <si>
-    <t>26.21mm</t>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>33.2mm</t>
+  </si>
+  <si>
+    <t>4.86mm</t>
+  </si>
+  <si>
+    <t>Top</t>
+  </si>
+  <si>
+    <t>270.0</t>
+  </si>
+  <si>
+    <t>K3</t>
+  </si>
+  <si>
+    <t>63.1mm</t>
+  </si>
+  <si>
+    <t>69.5mm</t>
   </si>
   <si>
     <t>Top</t>
   </si>
   <si>
     <t>90.0</t>
-  </si>
-  <si>
-    <t>J8</t>
-  </si>
-  <si>
-    <t>49.6mm</t>
-  </si>
-  <si>
-    <t>2.3mm</t>
-  </si>
-  <si>
-    <t>Top</t>
-  </si>
-  <si>
-    <t>0.0</t>
-  </si>
-  <si>
-    <t>J5</t>
-  </si>
-  <si>
-    <t>9.15mm</t>
-  </si>
-  <si>
-    <t>1.7mm</t>
-  </si>
-  <si>
-    <t>Top</t>
-  </si>
-  <si>
-    <t>0.0</t>
-  </si>
-  <si>
-    <t>J9</t>
-  </si>
-  <si>
-    <t>63.2mm</t>
-  </si>
-  <si>
-    <t>72.0mm</t>
-  </si>
-  <si>
-    <t>Top</t>
-  </si>
-  <si>
-    <t>90.0</t>
-  </si>
-  <si>
-    <t>X1</t>
-  </si>
-  <si>
-    <t>28.155mm</t>
-  </si>
-  <si>
-    <t>71.135mm</t>
-  </si>
-  <si>
-    <t>Top</t>
-  </si>
-  <si>
-    <t>270.0</t>
-  </si>
-  <si>
-    <t>K2</t>
-  </si>
-  <si>
-    <t>60.5mm</t>
-  </si>
-  <si>
-    <t>51.0mm</t>
-  </si>
-  <si>
-    <t>Top</t>
-  </si>
-  <si>
-    <t>0.0</t>
-  </si>
-  <si>
-    <t>IC2</t>
-  </si>
-  <si>
-    <t>49.7mm</t>
-  </si>
-  <si>
-    <t>23.525mm</t>
-  </si>
-  <si>
-    <t>Top</t>
-  </si>
-  <si>
-    <t>0.0</t>
-  </si>
-  <si>
-    <t>IC1</t>
-  </si>
-  <si>
-    <t>13.8mm</t>
-  </si>
-  <si>
-    <t>35.525mm</t>
-  </si>
-  <si>
-    <t>Top</t>
-  </si>
-  <si>
-    <t>0.0</t>
-  </si>
-  <si>
-    <t>J1</t>
-  </si>
-  <si>
-    <t>66.4mm</t>
-  </si>
-  <si>
-    <t>10.99mm</t>
-  </si>
-  <si>
-    <t>Top</t>
-  </si>
-  <si>
-    <t>270.0</t>
-  </si>
-  <si>
-    <t>J3</t>
-  </si>
-  <si>
-    <t>61.4mm</t>
-  </si>
-  <si>
-    <t>10.99mm</t>
-  </si>
-  <si>
-    <t>Top</t>
-  </si>
-  <si>
-    <t>270.0</t>
-  </si>
-  <si>
-    <t>J4</t>
-  </si>
-  <si>
-    <t>58.9mm</t>
-  </si>
-  <si>
-    <t>10.99mm</t>
-  </si>
-  <si>
-    <t>Top</t>
-  </si>
-  <si>
-    <t>270.0</t>
   </si>
 </sst>
 </file>
@@ -562,6 +622,74 @@
         <v>74</v>
       </c>
     </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" t="s">
+        <v>78</v>
+      </c>
+      <c r="E16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" t="s">
+        <v>88</v>
+      </c>
+      <c r="E18" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" t="s">
+        <v>93</v>
+      </c>
+      <c r="E19" t="s">
+        <v>94</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
